--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\rice_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C065ED0-DB16-4ACA-A927-A8A8F4610D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041C6B07-281A-48D4-B3BE-04D5D7B1CC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11484" yWindow="0" windowWidth="11556" windowHeight="12240" xr2:uid="{08C7E1D3-EFB9-46CA-8498-83E5013A38F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{08C7E1D3-EFB9-46CA-8498-83E5013A38F5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t>品種</t>
   </si>
@@ -371,6 +371,10 @@
   </si>
   <si>
     <t>圃場経度</t>
+  </si>
+  <si>
+    <t>湯浦</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -878,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550DFA4D-FD4A-4099-8CA6-1904B58900B2}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" customWidth="1"/>
@@ -1554,7 +1558,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="10">
         <v>80</v>
@@ -1605,6 +1609,65 @@
         <v>32.248600000000003</v>
       </c>
       <c r="S12" s="10">
+        <v>130.51329999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="10">
+        <v>80</v>
+      </c>
+      <c r="D13" s="10">
+        <v>-40</v>
+      </c>
+      <c r="E13" s="10">
+        <v>-24</v>
+      </c>
+      <c r="F13" s="10">
+        <v>-20</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-17</v>
+      </c>
+      <c r="H13" s="10">
+        <v>-10</v>
+      </c>
+      <c r="I13" s="10">
+        <v>10</v>
+      </c>
+      <c r="J13" s="10">
+        <v>25</v>
+      </c>
+      <c r="K13" s="10">
+        <v>33</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1050</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N13" s="10">
+        <v>6</v>
+      </c>
+      <c r="O13" s="10">
+        <v>200</v>
+      </c>
+      <c r="P13" s="10">
+        <v>32.200800000000001</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>130.40110000000001</v>
+      </c>
+      <c r="R13" s="10">
+        <v>32.248600000000003</v>
+      </c>
+      <c r="S13" s="10">
         <v>130.51329999999999</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\rice_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041C6B07-281A-48D4-B3BE-04D5D7B1CC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EC3E93-1B52-4F77-A261-4169301AB057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{08C7E1D3-EFB9-46CA-8498-83E5013A38F5}"/>
+    <workbookView xWindow="13056" yWindow="24" windowWidth="9912" windowHeight="12240" xr2:uid="{08C7E1D3-EFB9-46CA-8498-83E5013A38F5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
   <si>
     <t>品種</t>
   </si>
@@ -374,6 +374,10 @@
   </si>
   <si>
     <t>湯浦</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>赤松</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1558,7 +1562,7 @@
         <v>27</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="C12" s="10">
         <v>80</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\rice_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32EC3E93-1B52-4F77-A261-4169301AB057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C27E70-4B3A-4EBF-B6D1-D3701969CAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13056" yWindow="24" windowWidth="9912" windowHeight="12240" xr2:uid="{08C7E1D3-EFB9-46CA-8498-83E5013A38F5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>品種</t>
   </si>
@@ -377,7 +377,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>赤松</t>
+    <t>田浦</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>高岡</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1385,7 +1389,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C9" s="10">
         <v>75</v>
